--- a/profile_requirements.xlsx
+++ b/profile_requirements.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9436,6 +9436,331 @@
         <v>4</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Customer Focus</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Analytical &amp; Problem-Solving</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Digital Intelligence (DQ)</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Adaptability</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Initiative</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Glass Melting Process &amp; Furnace Operation</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Batch Preparation &amp; Batch Composition</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Process Control &amp; Process Stability</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Glass Quality &amp; Defect Analysis</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Raw Material Management / Optimization</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>268029 B</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Acting Department Manager - Batch and Furnace</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Furnace Performance &amp; Energy Efficiency</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
